--- a/artfynd/A 8666-2024 artfynd.xlsx
+++ b/artfynd/A 8666-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115196724</v>
+        <v>115196723</v>
       </c>
       <c r="B2" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>322348</v>
+        <v>322231</v>
       </c>
       <c r="R2" t="n">
-        <v>6461285</v>
+        <v>6461308</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115196723</v>
+        <v>115196724</v>
       </c>
       <c r="B3" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>322231</v>
+        <v>322348</v>
       </c>
       <c r="R3" t="n">
-        <v>6461308</v>
+        <v>6461285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115196726</v>
+        <v>115196725</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>322226</v>
+        <v>322204</v>
       </c>
       <c r="R4" t="n">
-        <v>6461331</v>
+        <v>6461280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,19 +971,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115196725</v>
+        <v>115196726</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1026,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>322204</v>
+        <v>322226</v>
       </c>
       <c r="R5" t="n">
-        <v>6461280</v>
+        <v>6461331</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1073,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115196728</v>
+        <v>115196727</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1133,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>322239</v>
+        <v>322231</v>
       </c>
       <c r="R6" t="n">
-        <v>6461271</v>
+        <v>6461308</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,19 +1175,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115196727</v>
+        <v>115196728</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1240,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>322231</v>
+        <v>322239</v>
       </c>
       <c r="R7" t="n">
-        <v>6461308</v>
+        <v>6461271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 8666-2024 artfynd.xlsx
+++ b/artfynd/A 8666-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196724</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196725</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196726</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196727</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,8 +1304,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115196728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>